--- a/htk_files/results/results_5_states/HMM_Results_5_states.xlsx
+++ b/htk_files/results/results_5_states/HMM_Results_5_states.xlsx
@@ -531,7 +531,7 @@
         <v>53.33</v>
       </c>
       <c r="L2" t="n">
-        <v>53.666</v>
+        <v>53.67</v>
       </c>
     </row>
     <row r="3">
@@ -571,7 +571,7 @@
         <v>63.33</v>
       </c>
       <c r="L3" t="n">
-        <v>56.33200000000001</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="4">
@@ -611,7 +611,7 @@
         <v>60</v>
       </c>
       <c r="L4" t="n">
-        <v>52.33199999999999</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="5">
@@ -651,7 +651,7 @@
         <v>50</v>
       </c>
       <c r="L5" t="n">
-        <v>52.33300000000001</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="6">
@@ -691,7 +691,7 @@
         <v>36.67</v>
       </c>
       <c r="L6" t="n">
-        <v>37.334</v>
+        <v>37.33</v>
       </c>
     </row>
     <row r="7">
@@ -731,7 +731,7 @@
         <v>53.33</v>
       </c>
       <c r="L7" t="n">
-        <v>48.334</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="8">
@@ -771,7 +771,7 @@
         <v>46.67</v>
       </c>
       <c r="L8" t="n">
-        <v>44.334</v>
+        <v>44.33</v>
       </c>
     </row>
     <row r="9">
@@ -811,7 +811,7 @@
         <v>53.33</v>
       </c>
       <c r="L9" t="n">
-        <v>45.33199999999999</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="10">
@@ -851,7 +851,7 @@
         <v>69.7</v>
       </c>
       <c r="L10" t="n">
-        <v>59.70000000000001</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="11">
@@ -891,7 +891,7 @@
         <v>54.55</v>
       </c>
       <c r="L11" t="n">
-        <v>54.246</v>
+        <v>54.25</v>
       </c>
     </row>
     <row r="12">
@@ -901,37 +901,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47.787</v>
+        <v>47.79</v>
       </c>
       <c r="C12" t="n">
-        <v>45.697</v>
+        <v>45.7</v>
       </c>
       <c r="D12" t="n">
-        <v>54.45500000000001</v>
+        <v>54.46</v>
       </c>
       <c r="E12" t="n">
-        <v>47.607</v>
+        <v>47.61</v>
       </c>
       <c r="F12" t="n">
-        <v>47.879</v>
+        <v>47.88</v>
       </c>
       <c r="G12" t="n">
-        <v>50.274</v>
+        <v>50.27</v>
       </c>
       <c r="H12" t="n">
-        <v>50.57700000000001</v>
+        <v>50.58</v>
       </c>
       <c r="I12" t="n">
-        <v>52.122</v>
+        <v>52.12</v>
       </c>
       <c r="J12" t="n">
-        <v>53.45399999999999</v>
+        <v>53.45</v>
       </c>
       <c r="K12" t="n">
-        <v>54.09099999999999</v>
+        <v>54.09</v>
       </c>
       <c r="L12" t="n">
-        <v>50.3943</v>
+        <v>50.39</v>
       </c>
     </row>
   </sheetData>
@@ -1042,7 +1042,7 @@
         <v>60</v>
       </c>
       <c r="L2" t="n">
-        <v>65.66800000000001</v>
+        <v>65.67</v>
       </c>
     </row>
     <row r="3">
@@ -1082,7 +1082,7 @@
         <v>43.33</v>
       </c>
       <c r="L3" t="n">
-        <v>38.001</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -1162,7 +1162,7 @@
         <v>43.33</v>
       </c>
       <c r="L5" t="n">
-        <v>42.333</v>
+        <v>42.33</v>
       </c>
     </row>
     <row r="6">
@@ -1202,7 +1202,7 @@
         <v>46.67</v>
       </c>
       <c r="L6" t="n">
-        <v>50.66800000000001</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="7">
@@ -1242,7 +1242,7 @@
         <v>53.33</v>
       </c>
       <c r="L7" t="n">
-        <v>51.33300000000001</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="8">
@@ -1282,7 +1282,7 @@
         <v>36.67</v>
       </c>
       <c r="L8" t="n">
-        <v>36.667</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="9">
@@ -1322,7 +1322,7 @@
         <v>72.73</v>
       </c>
       <c r="L9" t="n">
-        <v>55.153</v>
+        <v>55.15</v>
       </c>
     </row>
     <row r="10">
@@ -1362,7 +1362,7 @@
         <v>51.52</v>
       </c>
       <c r="L10" t="n">
-        <v>48.181</v>
+        <v>48.18</v>
       </c>
     </row>
     <row r="11">
@@ -1402,7 +1402,7 @@
         <v>44.44</v>
       </c>
       <c r="L11" t="n">
-        <v>51.48099999999999</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="12">
@@ -1412,19 +1412,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48.539</v>
+        <v>48.54</v>
       </c>
       <c r="C12" t="n">
-        <v>46.705</v>
+        <v>46.7</v>
       </c>
       <c r="D12" t="n">
-        <v>50.48199999999999</v>
+        <v>50.48</v>
       </c>
       <c r="E12" t="n">
-        <v>47.084</v>
+        <v>47.08</v>
       </c>
       <c r="F12" t="n">
-        <v>47.80099999999999</v>
+        <v>47.8</v>
       </c>
       <c r="G12" t="n">
         <v>47.66</v>
@@ -1433,16 +1433,16 @@
         <v>46.92</v>
       </c>
       <c r="I12" t="n">
-        <v>48.156</v>
+        <v>48.16</v>
       </c>
       <c r="J12" t="n">
-        <v>49.60299999999999</v>
+        <v>49.6</v>
       </c>
       <c r="K12" t="n">
-        <v>49.535</v>
+        <v>49.54</v>
       </c>
       <c r="L12" t="n">
-        <v>48.24849999999999</v>
+        <v>48.25</v>
       </c>
     </row>
   </sheetData>
@@ -1553,7 +1553,7 @@
         <v>63.33</v>
       </c>
       <c r="L2" t="n">
-        <v>60.66700000000001</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="3">
@@ -1633,7 +1633,7 @@
         <v>56.67</v>
       </c>
       <c r="L4" t="n">
-        <v>48.33199999999999</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="5">
@@ -1673,7 +1673,7 @@
         <v>50</v>
       </c>
       <c r="L5" t="n">
-        <v>45.999</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
@@ -1713,7 +1713,7 @@
         <v>30</v>
       </c>
       <c r="L6" t="n">
-        <v>39.334</v>
+        <v>39.33</v>
       </c>
     </row>
     <row r="7">
@@ -1753,7 +1753,7 @@
         <v>56.67</v>
       </c>
       <c r="L7" t="n">
-        <v>52.66799999999999</v>
+        <v>52.67</v>
       </c>
     </row>
     <row r="8">
@@ -1793,7 +1793,7 @@
         <v>36.67</v>
       </c>
       <c r="L8" t="n">
-        <v>36.66800000000001</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="9">
@@ -1833,7 +1833,7 @@
         <v>53.33</v>
       </c>
       <c r="L9" t="n">
-        <v>55.33300000000001</v>
+        <v>55.33</v>
       </c>
     </row>
     <row r="10">
@@ -1873,7 +1873,7 @@
         <v>51.52</v>
       </c>
       <c r="L10" t="n">
-        <v>54.851</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="11">
@@ -1913,7 +1913,7 @@
         <v>54.55</v>
       </c>
       <c r="L11" t="n">
-        <v>50.91099999999999</v>
+        <v>50.91</v>
       </c>
     </row>
     <row r="12">
@@ -1923,37 +1923,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51.424</v>
+        <v>51.42</v>
       </c>
       <c r="C12" t="n">
-        <v>49.182</v>
+        <v>49.18</v>
       </c>
       <c r="D12" t="n">
-        <v>45.062</v>
+        <v>45.06</v>
       </c>
       <c r="E12" t="n">
-        <v>48.75699999999999</v>
+        <v>48.76</v>
       </c>
       <c r="F12" t="n">
-        <v>49.001</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>51.214</v>
+        <v>51.21</v>
       </c>
       <c r="H12" t="n">
-        <v>51.879</v>
+        <v>51.88</v>
       </c>
       <c r="I12" t="n">
-        <v>52.69600000000001</v>
+        <v>52.7</v>
       </c>
       <c r="J12" t="n">
-        <v>52.94100000000001</v>
+        <v>52.94</v>
       </c>
       <c r="K12" t="n">
-        <v>52.60699999999999</v>
+        <v>52.61</v>
       </c>
       <c r="L12" t="n">
-        <v>50.47629999999999</v>
+        <v>50.48</v>
       </c>
     </row>
   </sheetData>
@@ -1967,7 +1967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2023,6 +2023,31 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11_gaussians</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>12_gaussians</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13_gaussians</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14_gaussians</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>15_gaussians</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>mean</t>
         </is>
       </c>
@@ -2064,7 +2089,22 @@
         <v>60</v>
       </c>
       <c r="L2" t="n">
-        <v>53.334</v>
+        <v>56.67</v>
+      </c>
+      <c r="M2" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="N2" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="O2" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="P2" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>55.78</v>
       </c>
     </row>
     <row r="3">
@@ -2104,7 +2144,22 @@
         <v>56.67</v>
       </c>
       <c r="L3" t="n">
-        <v>54.001</v>
+        <v>53.33</v>
+      </c>
+      <c r="M3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N3" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="O3" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="P3" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>54.22</v>
       </c>
     </row>
     <row r="4">
@@ -2144,7 +2199,22 @@
         <v>50</v>
       </c>
       <c r="L4" t="n">
-        <v>46</v>
+        <v>50</v>
+      </c>
+      <c r="M4" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="N4" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="O4" t="n">
+        <v>50</v>
+      </c>
+      <c r="P4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>46.67</v>
       </c>
     </row>
     <row r="5">
@@ -2184,7 +2254,22 @@
         <v>63.33</v>
       </c>
       <c r="L5" t="n">
-        <v>58.33300000000001</v>
+        <v>56.67</v>
+      </c>
+      <c r="M5" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="N5" t="n">
+        <v>60</v>
+      </c>
+      <c r="O5" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="P5" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>59.56</v>
       </c>
     </row>
     <row r="6">
@@ -2224,7 +2309,22 @@
         <v>36.67</v>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>33.33</v>
+      </c>
+      <c r="M6" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="N6" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="O6" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="P6" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>34.89</v>
       </c>
     </row>
     <row r="7">
@@ -2264,7 +2364,22 @@
         <v>66.67</v>
       </c>
       <c r="L7" t="n">
-        <v>51.33399999999999</v>
+        <v>60</v>
+      </c>
+      <c r="M7" t="n">
+        <v>60</v>
+      </c>
+      <c r="N7" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="O7" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="P7" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>54.22</v>
       </c>
     </row>
     <row r="8">
@@ -2304,7 +2419,22 @@
         <v>40</v>
       </c>
       <c r="L8" t="n">
-        <v>38.334</v>
+        <v>36.67</v>
+      </c>
+      <c r="M8" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="N8" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="O8" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="P8" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>38.44</v>
       </c>
     </row>
     <row r="9">
@@ -2344,7 +2474,22 @@
         <v>46.67</v>
       </c>
       <c r="L9" t="n">
-        <v>48.335</v>
+        <v>43.33</v>
+      </c>
+      <c r="M9" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="N9" t="n">
+        <v>50</v>
+      </c>
+      <c r="O9" t="n">
+        <v>50</v>
+      </c>
+      <c r="P9" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -2384,7 +2529,22 @@
         <v>72.73</v>
       </c>
       <c r="L10" t="n">
-        <v>62.427</v>
+        <v>69.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="N10" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="O10" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="P10" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>65.66</v>
       </c>
     </row>
     <row r="11">
@@ -2424,7 +2584,22 @@
         <v>51.52</v>
       </c>
       <c r="L11" t="n">
-        <v>50</v>
+        <v>54.55</v>
+      </c>
+      <c r="M11" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="N11" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="O11" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="P11" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>50.51</v>
       </c>
     </row>
     <row r="12">
@@ -2434,37 +2609,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45.121</v>
+        <v>45.12</v>
       </c>
       <c r="C12" t="n">
-        <v>44.275</v>
+        <v>44.28</v>
       </c>
       <c r="D12" t="n">
-        <v>48.547</v>
+        <v>48.55</v>
       </c>
       <c r="E12" t="n">
-        <v>48.425</v>
+        <v>48.42</v>
       </c>
       <c r="F12" t="n">
-        <v>48.578</v>
+        <v>48.58</v>
       </c>
       <c r="G12" t="n">
-        <v>50.817</v>
+        <v>50.82</v>
       </c>
       <c r="H12" t="n">
-        <v>51.48499999999999</v>
+        <v>51.48</v>
       </c>
       <c r="I12" t="n">
-        <v>52.242</v>
+        <v>52.24</v>
       </c>
       <c r="J12" t="n">
-        <v>53.182</v>
+        <v>53.18</v>
       </c>
       <c r="K12" t="n">
-        <v>54.426</v>
+        <v>54.43</v>
       </c>
       <c r="L12" t="n">
-        <v>49.7098</v>
+        <v>51.42</v>
+      </c>
+      <c r="M12" t="n">
+        <v>52.09</v>
+      </c>
+      <c r="N12" t="n">
+        <v>53.12</v>
+      </c>
+      <c r="O12" t="n">
+        <v>53.46</v>
+      </c>
+      <c r="P12" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>50.79</v>
       </c>
     </row>
   </sheetData>
@@ -2615,7 +2805,7 @@
         <v>56.67</v>
       </c>
       <c r="L3" t="n">
-        <v>51.334</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="4">
@@ -2655,7 +2845,7 @@
         <v>53.33</v>
       </c>
       <c r="L4" t="n">
-        <v>56.33300000000001</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="5">
@@ -2695,7 +2885,7 @@
         <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>42.334</v>
+        <v>42.33</v>
       </c>
     </row>
     <row r="6">
@@ -2775,7 +2965,7 @@
         <v>56.67</v>
       </c>
       <c r="L7" t="n">
-        <v>52.334</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="8">
@@ -2815,7 +3005,7 @@
         <v>30</v>
       </c>
       <c r="L8" t="n">
-        <v>38.334</v>
+        <v>38.33</v>
       </c>
     </row>
     <row r="9">
@@ -2855,7 +3045,7 @@
         <v>45.45</v>
       </c>
       <c r="L9" t="n">
-        <v>50.60600000000001</v>
+        <v>50.61</v>
       </c>
     </row>
     <row r="10">
@@ -2895,7 +3085,7 @@
         <v>64.09999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>58.717</v>
+        <v>58.72</v>
       </c>
     </row>
     <row r="11">
@@ -2935,7 +3125,7 @@
         <v>44.44</v>
       </c>
       <c r="L11" t="n">
-        <v>46.666</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="12">
@@ -2945,37 +3135,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50.544</v>
+        <v>50.54</v>
       </c>
       <c r="C12" t="n">
-        <v>46.218</v>
+        <v>46.22</v>
       </c>
       <c r="D12" t="n">
-        <v>48.219</v>
+        <v>48.22</v>
       </c>
       <c r="E12" t="n">
-        <v>51.02200000000001</v>
+        <v>51.02</v>
       </c>
       <c r="F12" t="n">
-        <v>50.282</v>
+        <v>50.28</v>
       </c>
       <c r="G12" t="n">
-        <v>50.61499999999999</v>
+        <v>50.61</v>
       </c>
       <c r="H12" t="n">
-        <v>49.55200000000001</v>
+        <v>49.55</v>
       </c>
       <c r="I12" t="n">
-        <v>50.263</v>
+        <v>50.26</v>
       </c>
       <c r="J12" t="n">
-        <v>50.211</v>
+        <v>50.21</v>
       </c>
       <c r="K12" t="n">
-        <v>48.732</v>
+        <v>48.73</v>
       </c>
       <c r="L12" t="n">
-        <v>49.5658</v>
+        <v>49.57</v>
       </c>
     </row>
   </sheetData>
@@ -2989,7 +3179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3045,6 +3235,31 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11_gaussians</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>12_gaussians</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13_gaussians</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14_gaussians</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>15_gaussians</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>mean</t>
         </is>
       </c>
@@ -3086,7 +3301,22 @@
         <v>70</v>
       </c>
       <c r="L2" t="n">
-        <v>56.998</v>
+        <v>63.33</v>
+      </c>
+      <c r="M2" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="N2" t="n">
+        <v>50</v>
+      </c>
+      <c r="O2" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="P2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -3126,7 +3356,22 @@
         <v>66.67</v>
       </c>
       <c r="L3" t="n">
-        <v>58.99999999999999</v>
+        <v>53.33</v>
+      </c>
+      <c r="M3" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="N3" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="O3" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="P3" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="4">
@@ -3166,7 +3411,22 @@
         <v>50</v>
       </c>
       <c r="L4" t="n">
-        <v>45.001</v>
+        <v>53.33</v>
+      </c>
+      <c r="M4" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="N4" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="O4" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="P4" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>47.78</v>
       </c>
     </row>
     <row r="5">
@@ -3206,7 +3466,22 @@
         <v>46.67</v>
       </c>
       <c r="L5" t="n">
-        <v>47.334</v>
+        <v>50</v>
+      </c>
+      <c r="M5" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="N5" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="O5" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="P5" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>46.67</v>
       </c>
     </row>
     <row r="6">
@@ -3246,7 +3521,22 @@
         <v>36.67</v>
       </c>
       <c r="L6" t="n">
-        <v>38.334</v>
+        <v>36.67</v>
+      </c>
+      <c r="M6" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="N6" t="n">
+        <v>30</v>
+      </c>
+      <c r="O6" t="n">
+        <v>30</v>
+      </c>
+      <c r="P6" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>36.22</v>
       </c>
     </row>
     <row r="7">
@@ -3286,7 +3576,22 @@
         <v>60</v>
       </c>
       <c r="L7" t="n">
-        <v>55.66700000000001</v>
+        <v>63.33</v>
+      </c>
+      <c r="M7" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="N7" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="O7" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="P7" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="8">
@@ -3326,7 +3631,22 @@
         <v>43.33</v>
       </c>
       <c r="L8" t="n">
-        <v>41.667</v>
+        <v>43.33</v>
+      </c>
+      <c r="M8" t="n">
+        <v>40</v>
+      </c>
+      <c r="N8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O8" t="n">
+        <v>40</v>
+      </c>
+      <c r="P8" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>41.33</v>
       </c>
     </row>
     <row r="9">
@@ -3366,7 +3686,22 @@
         <v>57.58</v>
       </c>
       <c r="L9" t="n">
-        <v>56.367</v>
+        <v>57.58</v>
+      </c>
+      <c r="M9" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="N9" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="O9" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="P9" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>56.57</v>
       </c>
     </row>
     <row r="10">
@@ -3406,7 +3741,22 @@
         <v>58.97</v>
       </c>
       <c r="L10" t="n">
-        <v>54.101</v>
+        <v>61.54</v>
+      </c>
+      <c r="M10" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="N10" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="O10" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="P10" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>57.26</v>
       </c>
     </row>
     <row r="11">
@@ -3446,7 +3796,22 @@
         <v>66.67</v>
       </c>
       <c r="L11" t="n">
-        <v>60</v>
+        <v>70.37</v>
+      </c>
+      <c r="M11" t="n">
+        <v>62.96</v>
+      </c>
+      <c r="N11" t="n">
+        <v>62.96</v>
+      </c>
+      <c r="O11" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="P11" t="n">
+        <v>62.96</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>61.23</v>
       </c>
     </row>
     <row r="12">
@@ -3456,37 +3821,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49.586</v>
+        <v>49.59</v>
       </c>
       <c r="C12" t="n">
-        <v>49.477</v>
+        <v>49.48</v>
       </c>
       <c r="D12" t="n">
-        <v>47.825</v>
+        <v>47.82</v>
       </c>
       <c r="E12" t="n">
-        <v>50.033</v>
+        <v>50.03</v>
       </c>
       <c r="F12" t="n">
-        <v>52.33899999999998</v>
+        <v>52.34</v>
       </c>
       <c r="G12" t="n">
-        <v>54.73199999999999</v>
+        <v>54.73</v>
       </c>
       <c r="H12" t="n">
-        <v>50.581</v>
+        <v>50.58</v>
       </c>
       <c r="I12" t="n">
-        <v>51.878</v>
+        <v>51.88</v>
       </c>
       <c r="J12" t="n">
-        <v>52.362</v>
+        <v>52.36</v>
       </c>
       <c r="K12" t="n">
-        <v>55.65599999999999</v>
+        <v>55.66</v>
       </c>
       <c r="L12" t="n">
-        <v>51.44690000000001</v>
+        <v>55.28</v>
+      </c>
+      <c r="M12" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="N12" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="O12" t="n">
+        <v>52.76</v>
+      </c>
+      <c r="P12" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>51.91</v>
       </c>
     </row>
   </sheetData>
@@ -3637,7 +4017,7 @@
         <v>63.33</v>
       </c>
       <c r="L3" t="n">
-        <v>62.66700000000001</v>
+        <v>62.67</v>
       </c>
     </row>
     <row r="4">
@@ -3677,7 +4057,7 @@
         <v>56.67</v>
       </c>
       <c r="L4" t="n">
-        <v>52.334</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="5">
@@ -3797,7 +4177,7 @@
         <v>50</v>
       </c>
       <c r="L7" t="n">
-        <v>47.66800000000001</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="8">
@@ -3837,7 +4217,7 @@
         <v>43.33</v>
       </c>
       <c r="L8" t="n">
-        <v>45.333</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="9">
@@ -3877,7 +4257,7 @@
         <v>51.52</v>
       </c>
       <c r="L9" t="n">
-        <v>50.302</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="10">
@@ -3917,7 +4297,7 @@
         <v>56.41</v>
       </c>
       <c r="L10" t="n">
-        <v>57.435</v>
+        <v>57.44</v>
       </c>
     </row>
     <row r="11">
@@ -3957,7 +4337,7 @@
         <v>70.37</v>
       </c>
       <c r="L11" t="n">
-        <v>65.556</v>
+        <v>65.56</v>
       </c>
     </row>
     <row r="12">
@@ -3967,37 +4347,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52.68300000000001</v>
+        <v>52.68</v>
       </c>
       <c r="C12" t="n">
-        <v>54.535</v>
+        <v>54.54</v>
       </c>
       <c r="D12" t="n">
-        <v>50.696</v>
+        <v>50.7</v>
       </c>
       <c r="E12" t="n">
-        <v>51.36899999999999</v>
+        <v>51.37</v>
       </c>
       <c r="F12" t="n">
-        <v>49.772</v>
+        <v>49.77</v>
       </c>
       <c r="G12" t="n">
-        <v>52.782</v>
+        <v>52.78</v>
       </c>
       <c r="H12" t="n">
-        <v>54.03900000000001</v>
+        <v>54.04</v>
       </c>
       <c r="I12" t="n">
-        <v>54.146</v>
+        <v>54.15</v>
       </c>
       <c r="J12" t="n">
-        <v>53.776</v>
+        <v>53.78</v>
       </c>
       <c r="K12" t="n">
-        <v>54.497</v>
+        <v>54.5</v>
       </c>
       <c r="L12" t="n">
-        <v>52.8295</v>
+        <v>52.83</v>
       </c>
     </row>
   </sheetData>
@@ -4108,7 +4488,7 @@
         <v>70</v>
       </c>
       <c r="L2" t="n">
-        <v>55.334</v>
+        <v>55.33</v>
       </c>
     </row>
     <row r="3">
@@ -4148,7 +4528,7 @@
         <v>46.67</v>
       </c>
       <c r="L3" t="n">
-        <v>49.335</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="4">
@@ -4228,7 +4608,7 @@
         <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>44.333</v>
+        <v>44.33</v>
       </c>
     </row>
     <row r="6">
@@ -4268,7 +4648,7 @@
         <v>60</v>
       </c>
       <c r="L6" t="n">
-        <v>53.001</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -4308,7 +4688,7 @@
         <v>56.67</v>
       </c>
       <c r="L7" t="n">
-        <v>57.66799999999999</v>
+        <v>57.67</v>
       </c>
     </row>
     <row r="8">
@@ -4348,7 +4728,7 @@
         <v>43.33</v>
       </c>
       <c r="L8" t="n">
-        <v>46.666</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="9">
@@ -4388,7 +4768,7 @@
         <v>60.61</v>
       </c>
       <c r="L9" t="n">
-        <v>58.488</v>
+        <v>58.49</v>
       </c>
     </row>
     <row r="10">
@@ -4428,7 +4808,7 @@
         <v>64.09999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>58.20400000000001</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="11">
@@ -4468,7 +4848,7 @@
         <v>37.04</v>
       </c>
       <c r="L11" t="n">
-        <v>37.408</v>
+        <v>37.41</v>
       </c>
     </row>
     <row r="12">
@@ -4478,37 +4858,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47.96400000000001</v>
+        <v>47.96</v>
       </c>
       <c r="C12" t="n">
-        <v>53.148</v>
+        <v>53.15</v>
       </c>
       <c r="D12" t="n">
-        <v>48.514</v>
+        <v>48.51</v>
       </c>
       <c r="E12" t="n">
-        <v>48.66100000000001</v>
+        <v>48.66</v>
       </c>
       <c r="F12" t="n">
         <v>51.42</v>
       </c>
       <c r="G12" t="n">
-        <v>52.807</v>
+        <v>52.81</v>
       </c>
       <c r="H12" t="n">
-        <v>49.063</v>
+        <v>49.06</v>
       </c>
       <c r="I12" t="n">
-        <v>51.842</v>
+        <v>51.84</v>
       </c>
       <c r="J12" t="n">
-        <v>51.843</v>
+        <v>51.84</v>
       </c>
       <c r="K12" t="n">
-        <v>53.175</v>
+        <v>53.18</v>
       </c>
       <c r="L12" t="n">
-        <v>50.8437</v>
+        <v>50.84</v>
       </c>
     </row>
   </sheetData>
@@ -4659,7 +5039,7 @@
         <v>63.33</v>
       </c>
       <c r="L3" t="n">
-        <v>58.00100000000001</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
@@ -4699,7 +5079,7 @@
         <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>41.66800000000001</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="5">
@@ -4739,7 +5119,7 @@
         <v>50</v>
       </c>
       <c r="L5" t="n">
-        <v>46.66800000000001</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="6">
@@ -4819,7 +5199,7 @@
         <v>60</v>
       </c>
       <c r="L7" t="n">
-        <v>54.334</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="8">
@@ -4899,7 +5279,7 @@
         <v>69.7</v>
       </c>
       <c r="L9" t="n">
-        <v>59.396</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="10">
@@ -4939,7 +5319,7 @@
         <v>64.09999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>60.76700000000001</v>
+        <v>60.77</v>
       </c>
     </row>
     <row r="11">
@@ -4979,7 +5359,7 @@
         <v>40.74</v>
       </c>
       <c r="L11" t="n">
-        <v>42.22199999999999</v>
+        <v>42.22</v>
       </c>
     </row>
     <row r="12">
@@ -4989,37 +5369,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49.188</v>
+        <v>49.19</v>
       </c>
       <c r="C12" t="n">
-        <v>48.027</v>
+        <v>48.03</v>
       </c>
       <c r="D12" t="n">
-        <v>48.69500000000001</v>
+        <v>48.7</v>
       </c>
       <c r="E12" t="n">
-        <v>47.426</v>
+        <v>47.43</v>
       </c>
       <c r="F12" t="n">
-        <v>49.16699999999999</v>
+        <v>49.17</v>
       </c>
       <c r="G12" t="n">
-        <v>52.22000000000001</v>
+        <v>52.22</v>
       </c>
       <c r="H12" t="n">
-        <v>51.637</v>
+        <v>51.64</v>
       </c>
       <c r="I12" t="n">
-        <v>53.349</v>
+        <v>53.35</v>
       </c>
       <c r="J12" t="n">
-        <v>53.89299999999999</v>
+        <v>53.89</v>
       </c>
       <c r="K12" t="n">
-        <v>54.45399999999999</v>
+        <v>54.45</v>
       </c>
       <c r="L12" t="n">
-        <v>50.8056</v>
+        <v>50.81</v>
       </c>
     </row>
   </sheetData>
@@ -5033,7 +5413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5089,6 +5469,31 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11_gaussians</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>12_gaussians</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13_gaussians</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14_gaussians</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>15_gaussians</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>mean</t>
         </is>
       </c>
@@ -5130,7 +5535,22 @@
         <v>53.33</v>
       </c>
       <c r="L2" t="n">
-        <v>56.665</v>
+        <v>53.33</v>
+      </c>
+      <c r="M2" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="N2" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="O2" t="n">
+        <v>60</v>
+      </c>
+      <c r="P2" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>56.89</v>
       </c>
     </row>
     <row r="3">
@@ -5170,7 +5590,22 @@
         <v>46.67</v>
       </c>
       <c r="L3" t="n">
-        <v>44.334</v>
+        <v>40</v>
+      </c>
+      <c r="M3" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="N3" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="O3" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="P3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>44.22</v>
       </c>
     </row>
     <row r="4">
@@ -5210,7 +5645,22 @@
         <v>50</v>
       </c>
       <c r="L4" t="n">
-        <v>44.667</v>
+        <v>50</v>
+      </c>
+      <c r="M4" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="N4" t="n">
+        <v>50</v>
+      </c>
+      <c r="O4" t="n">
+        <v>50</v>
+      </c>
+      <c r="P4" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>46.44</v>
       </c>
     </row>
     <row r="5">
@@ -5250,7 +5700,22 @@
         <v>56.67</v>
       </c>
       <c r="L5" t="n">
-        <v>49.334</v>
+        <v>53.33</v>
+      </c>
+      <c r="M5" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="N5" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="O5" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="P5" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>51.33</v>
       </c>
     </row>
     <row r="6">
@@ -5290,7 +5755,22 @@
         <v>56.67</v>
       </c>
       <c r="L6" t="n">
-        <v>54.33299999999999</v>
+        <v>53.33</v>
+      </c>
+      <c r="M6" t="n">
+        <v>60</v>
+      </c>
+      <c r="N6" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="O6" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="P6" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>55.56</v>
       </c>
     </row>
     <row r="7">
@@ -5330,7 +5810,22 @@
         <v>56.67</v>
       </c>
       <c r="L7" t="n">
-        <v>56.666</v>
+        <v>50</v>
+      </c>
+      <c r="M7" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="N7" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="O7" t="n">
+        <v>50</v>
+      </c>
+      <c r="P7" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>54.89</v>
       </c>
     </row>
     <row r="8">
@@ -5370,7 +5865,22 @@
         <v>53.33</v>
       </c>
       <c r="L8" t="n">
-        <v>47.332</v>
+        <v>53.33</v>
+      </c>
+      <c r="M8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N8" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="O8" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="P8" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>47.33</v>
       </c>
     </row>
     <row r="9">
@@ -5410,7 +5920,22 @@
         <v>66.67</v>
       </c>
       <c r="L9" t="n">
-        <v>60.609</v>
+        <v>66.67</v>
+      </c>
+      <c r="M9" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="N9" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="O9" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="P9" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>61.62</v>
       </c>
     </row>
     <row r="10">
@@ -5450,7 +5975,22 @@
         <v>69.7</v>
       </c>
       <c r="L10" t="n">
-        <v>58.184</v>
+        <v>66.67</v>
+      </c>
+      <c r="M10" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="N10" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="O10" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="P10" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>62.22</v>
       </c>
     </row>
     <row r="11">
@@ -5490,7 +6030,22 @@
         <v>62.96</v>
       </c>
       <c r="L11" t="n">
-        <v>56.29599999999999</v>
+        <v>62.96</v>
+      </c>
+      <c r="M11" t="n">
+        <v>62.96</v>
+      </c>
+      <c r="N11" t="n">
+        <v>62.96</v>
+      </c>
+      <c r="O11" t="n">
+        <v>62.96</v>
+      </c>
+      <c r="P11" t="n">
+        <v>62.96</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>58.52</v>
       </c>
     </row>
     <row r="12">
@@ -5500,37 +6055,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52.75100000000001</v>
+        <v>52.75</v>
       </c>
       <c r="C12" t="n">
-        <v>48.725</v>
+        <v>48.72</v>
       </c>
       <c r="D12" t="n">
-        <v>52.76800000000001</v>
+        <v>52.77</v>
       </c>
       <c r="E12" t="n">
-        <v>53.078</v>
+        <v>53.08</v>
       </c>
       <c r="F12" t="n">
         <v>48.85</v>
       </c>
       <c r="G12" t="n">
-        <v>51.568</v>
+        <v>51.57</v>
       </c>
       <c r="H12" t="n">
-        <v>54.751</v>
+        <v>54.75</v>
       </c>
       <c r="I12" t="n">
-        <v>53.698</v>
+        <v>53.7</v>
       </c>
       <c r="J12" t="n">
-        <v>54.964</v>
+        <v>54.96</v>
       </c>
       <c r="K12" t="n">
-        <v>57.267</v>
+        <v>57.27</v>
       </c>
       <c r="L12" t="n">
-        <v>52.84200000000001</v>
+        <v>54.96</v>
+      </c>
+      <c r="M12" t="n">
+        <v>56.02</v>
+      </c>
+      <c r="N12" t="n">
+        <v>56.93</v>
+      </c>
+      <c r="O12" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="P12" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>53.9</v>
       </c>
     </row>
   </sheetData>
